--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -195,13 +195,13 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
@@ -958,7 +958,7 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -1021,7 +1021,7 @@
         <v>-1</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -1848,7 +1848,7 @@
         <v>-1</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1911,7 +1911,7 @@
         <v>-1</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -2471,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2534,7 +2534,7 @@
         <v>-1</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2649,7 +2649,7 @@
         <v>-1</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2712,7 +2712,7 @@
         <v>-1</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2738,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2801,7 +2801,7 @@
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2827,7 +2827,7 @@
         <v>-1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>-1</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -3005,7 +3005,7 @@
         <v>-1</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3068,7 +3068,7 @@
         <v>-1</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -3094,7 +3094,7 @@
         <v>-1</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3157,7 +3157,7 @@
         <v>-1</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3183,7 +3183,7 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -3246,7 +3246,7 @@
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>5</v>
@@ -3272,7 +3272,7 @@
         <v>-1</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3335,7 +3335,7 @@
         <v>-1</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>5</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G4">
         <v>70</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="G21">
         <v>85</v>
@@ -5042,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="G25">
         <v>90</v>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>55</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="G28">
         <v>95</v>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="G29">
         <v>90</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5927,30 +5927,30 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>63.33</v>
+        <v>80</v>
       </c>
       <c r="G5">
-        <v>3.33</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5959,19 +5959,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5991,19 +5991,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="G7">
-        <v>16.67</v>
+        <v>6.67</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6051,7 +6051,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6092,24 +6092,24 @@
         <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6120,16 +6120,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920263</v>
+        <v>22330051920262</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6140,16 +6140,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920262</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6160,16 +6160,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6180,16 +6180,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920264</v>
+        <v>22330051920403</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6200,16 +6200,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920403</v>
+        <v>22330051920404</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6220,16 +6220,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920404</v>
+        <v>22330051920409</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6240,16 +6240,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920409</v>
+        <v>22330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6260,16 +6260,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6280,16 +6280,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920411</v>
+        <v>22330051920405</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -6300,36 +6300,36 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920405</v>
+        <v>22330051920266</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920405</v>
+        <v>22330051920268</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6340,16 +6340,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920266</v>
+        <v>22330051920270</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -6360,16 +6360,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920268</v>
+        <v>22330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6380,16 +6380,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920270</v>
+        <v>22330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -6400,16 +6400,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920271</v>
+        <v>22330051920367</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -6420,16 +6420,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920272</v>
+        <v>22330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -6440,36 +6440,36 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920367</v>
+        <v>22330051920406</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920367</v>
+        <v>22330051920276</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -6480,16 +6480,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920273</v>
+        <v>22330051920281</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -6500,16 +6500,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920406</v>
+        <v>22330051920277</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -6520,36 +6520,36 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920276</v>
+        <v>22330051920395</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920276</v>
+        <v>22330051920279</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -6560,36 +6560,36 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920281</v>
+        <v>22330051920407</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920281</v>
+        <v>22330051920282</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -6600,36 +6600,36 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920277</v>
+        <v>22330051920283</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920277</v>
+        <v>22330051920285</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -6640,16 +6640,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920395</v>
+        <v>22330051920286</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -6660,221 +6660,21 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920279</v>
+        <v>22330051920288</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920279</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920407</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920407</v>
-      </c>
-      <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920282</v>
-      </c>
-      <c r="B35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920282</v>
-      </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920283</v>
-      </c>
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920283</v>
-      </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920285</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920286</v>
-      </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920288</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6923,174 +6723,174 @@
         <v>113</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920405</v>
+        <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920367</v>
+        <v>22330051920262</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920276</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920281</v>
+        <v>22330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920277</v>
+        <v>22330051920403</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920407</v>
+        <v>22330051920409</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920282</v>
+        <v>22330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920283</v>
+        <v>22330051920411</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920263</v>
+        <v>22330051920405</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -7098,16 +6898,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920262</v>
+        <v>22330051920266</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -7115,16 +6915,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920402</v>
+        <v>22330051920268</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -7132,16 +6932,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920264</v>
+        <v>22330051920270</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -7149,16 +6949,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920403</v>
+        <v>22330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -7166,16 +6966,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920404</v>
+        <v>22330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -7183,16 +6983,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920409</v>
+        <v>22330051920367</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -7200,16 +7000,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920265</v>
+        <v>22330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -7217,16 +7017,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920411</v>
+        <v>22330051920406</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -7234,16 +7034,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920266</v>
+        <v>22330051920276</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -7251,16 +7051,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920268</v>
+        <v>22330051920281</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -7268,16 +7068,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920270</v>
+        <v>22330051920277</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -7285,16 +7085,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920271</v>
+        <v>22330051920395</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -7302,16 +7102,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920272</v>
+        <v>22330051920279</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -7319,16 +7119,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920273</v>
+        <v>22330051920407</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -7336,16 +7136,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920406</v>
+        <v>22330051920282</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -7353,16 +7153,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920395</v>
+        <v>22330051920283</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -7426,7 +7226,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7611,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7734,62 +7534,62 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920285</v>
+        <v>22330051920276</v>
       </c>
       <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
         <v>91</v>
       </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920285</v>
+        <v>22330051920276</v>
       </c>
       <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
         <v>91</v>
       </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920286</v>
+        <v>22330051920407</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -7803,16 +7603,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920286</v>
+        <v>22330051920407</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7826,16 +7626,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920288</v>
+        <v>22330051920282</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -7849,16 +7649,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920288</v>
+        <v>22330051920282</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -7872,39 +7672,39 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920409</v>
+        <v>22330051920285</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920411</v>
+        <v>22330051920285</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -7918,16 +7718,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920266</v>
+        <v>22330051920286</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -7941,39 +7741,39 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920271</v>
+        <v>22330051920286</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920272</v>
+        <v>22330051920288</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -7987,24 +7787,162 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
+        <v>22330051920288</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920409</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920411</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920266</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920271</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920272</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
         <v>22330051920406</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B31" t="s">
         <v>83</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C31" t="s">
         <v>87</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D31" t="s">
         <v>130</v>
       </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
         <v>55</v>
       </c>
-      <c r="G25">
+      <c r="G31">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -186,10 +186,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -955,7 +955,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -1018,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -1044,7 +1044,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1222,7 +1222,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -1285,7 +1285,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -1311,7 +1311,7 @@
         <v>6</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>9</v>
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1400,7 +1400,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>5</v>
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1552,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1578,7 +1578,7 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>9</v>
@@ -1641,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1667,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>9</v>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -1756,7 +1756,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1819,7 +1819,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -1845,7 +1845,7 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -1908,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1934,7 +1934,7 @@
         <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -2023,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -2086,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2112,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>9</v>
@@ -2175,7 +2175,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2201,7 +2201,7 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -2264,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2290,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2353,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2379,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2442,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2468,7 +2468,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>6</v>
@@ -2531,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2557,7 +2557,7 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2646,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>8</v>
@@ -2798,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2824,7 +2824,7 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>6</v>
@@ -2887,7 +2887,7 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>6</v>
@@ -2913,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2976,7 +2976,7 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>6</v>
@@ -3002,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -3091,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F28">
         <v>7</v>
@@ -3154,7 +3154,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3180,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -3243,7 +3243,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3269,7 +3269,7 @@
         <v>5</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>6</v>
@@ -3332,7 +3332,7 @@
         <v>5</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3358,7 +3358,7 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>9</v>
@@ -3421,7 +3421,7 @@
         <v>5</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3447,7 +3447,7 @@
         <v>6</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F32">
         <v>9</v>
@@ -3510,7 +3510,7 @@
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -3536,7 +3536,7 @@
         <v>6</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>9</v>
@@ -3599,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -3747,7 +3747,7 @@
         <v>96</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F4">
         <v>120</v>
@@ -3815,7 +3815,7 @@
         <v>96</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>120</v>
@@ -3883,7 +3883,7 @@
         <v>96</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>120</v>
@@ -3951,7 +3951,7 @@
         <v>96</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F7">
         <v>120</v>
@@ -4019,7 +4019,7 @@
         <v>96</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F8">
         <v>120</v>
@@ -4087,7 +4087,7 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>96</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F10">
         <v>120</v>
@@ -4223,7 +4223,7 @@
         <v>96</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F11">
         <v>120</v>
@@ -4291,7 +4291,7 @@
         <v>96</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F12">
         <v>120</v>
@@ -4359,7 +4359,7 @@
         <v>96</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F13">
         <v>120</v>
@@ -4427,7 +4427,7 @@
         <v>84</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4495,7 +4495,7 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F15">
         <v>120</v>
@@ -4563,7 +4563,7 @@
         <v>96</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>120</v>
@@ -4631,7 +4631,7 @@
         <v>96</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F17">
         <v>120</v>
@@ -4699,7 +4699,7 @@
         <v>96</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F18">
         <v>120</v>
@@ -4767,7 +4767,7 @@
         <v>96</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F19">
         <v>120</v>
@@ -4835,7 +4835,7 @@
         <v>96</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F20">
         <v>120</v>
@@ -4903,7 +4903,7 @@
         <v>96</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F21">
         <v>113.3</v>
@@ -4971,7 +4971,7 @@
         <v>96</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F22">
         <v>120</v>
@@ -5039,7 +5039,7 @@
         <v>96</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F23">
         <v>120</v>
@@ -5107,7 +5107,7 @@
         <v>96</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F24">
         <v>120</v>
@@ -5175,7 +5175,7 @@
         <v>96</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F25">
         <v>106.7</v>
@@ -5243,7 +5243,7 @@
         <v>96</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>120</v>
@@ -5311,7 +5311,7 @@
         <v>80</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -5379,7 +5379,7 @@
         <v>96</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F28">
         <v>106.7</v>
@@ -5447,7 +5447,7 @@
         <v>96</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F29">
         <v>113.3</v>
@@ -5515,7 +5515,7 @@
         <v>76</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F30">
         <v>93.3</v>
@@ -5583,7 +5583,7 @@
         <v>96</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>120</v>
@@ -5651,7 +5651,7 @@
         <v>96</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F32">
         <v>120</v>
@@ -5719,7 +5719,7 @@
         <v>96</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F33">
         <v>120</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5834,27 +5834,30 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.67</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>73.33</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5863,19 +5866,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>26.67</v>
+        <v>36.67</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>63.33</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6051,7 +6054,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6076,606 +6079,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920396</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920263</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920262</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920402</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920264</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920403</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920404</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920409</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920265</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920411</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920405</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920266</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920268</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920270</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920271</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920272</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920367</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920273</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920406</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920276</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920281</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920277</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920395</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920279</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920407</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920282</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920283</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920285</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920286</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>140</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920288</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -6723,7 +6126,7 @@
         <v>113</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6740,7 +6143,7 @@
         <v>114</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6757,7 +6160,7 @@
         <v>115</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6774,7 +6177,7 @@
         <v>116</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6791,7 +6194,7 @@
         <v>117</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6808,7 +6211,7 @@
         <v>118</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6825,7 +6228,7 @@
         <v>119</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6842,7 +6245,7 @@
         <v>120</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6859,7 +6262,7 @@
         <v>121</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6876,7 +6279,7 @@
         <v>122</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6893,7 +6296,7 @@
         <v>123</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6910,7 +6313,7 @@
         <v>124</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6927,7 +6330,7 @@
         <v>125</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6944,7 +6347,7 @@
         <v>126</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6961,7 +6364,7 @@
         <v>127</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6978,7 +6381,7 @@
         <v>128</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6995,7 +6398,7 @@
         <v>129</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7012,7 +6415,7 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7029,7 +6432,7 @@
         <v>130</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7046,7 +6449,7 @@
         <v>131</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7063,7 +6466,7 @@
         <v>132</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7080,7 +6483,7 @@
         <v>133</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7097,7 +6500,7 @@
         <v>134</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7114,7 +6517,7 @@
         <v>135</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7131,7 +6534,7 @@
         <v>136</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7148,7 +6551,7 @@
         <v>137</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7165,7 +6568,7 @@
         <v>138</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7182,7 +6585,7 @@
         <v>139</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7199,7 +6602,7 @@
         <v>140</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7216,7 +6619,7 @@
         <v>141</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7226,7 +6629,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7273,10 +6676,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -7296,7 +6699,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7304,45 +6707,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920264</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920264</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7350,45 +6753,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7396,22 +6799,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920268</v>
+        <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7419,68 +6822,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920268</v>
+        <v>22330051920276</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920270</v>
+        <v>22330051920277</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920270</v>
+        <v>22330051920277</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7488,45 +6891,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920273</v>
+        <v>22330051920282</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920273</v>
+        <v>22330051920282</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7534,42 +6937,42 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920276</v>
+        <v>22330051920285</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920276</v>
+        <v>22330051920285</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>56</v>
@@ -7580,42 +6983,42 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920407</v>
+        <v>22330051920264</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>55</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920407</v>
+        <v>22330051920409</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>56</v>
@@ -7626,45 +7029,45 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920282</v>
+        <v>22330051920411</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920282</v>
+        <v>22330051920268</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -7672,22 +7075,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920285</v>
+        <v>22330051920272</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -7695,48 +7098,48 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920285</v>
+        <v>22330051920273</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>55</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920286</v>
+        <v>22330051920407</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
         <v>55</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7756,7 +7159,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -7776,174 +7179,13 @@
         <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
       </c>
       <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920288</v>
-      </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920409</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920411</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920266</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920271</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920272</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920406</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -195,6 +194,9 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -204,9 +206,6 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -219,223 +218,106 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>CARRERA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ALDO</t>
   </si>
   <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>YAZMIN SINAI</t>
-  </si>
-  <si>
-    <t>ZAID RAUL</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
     <t>OZIEL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
   </si>
   <si>
     <t>QUETZALY</t>
@@ -451,6 +333,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -503,11 +388,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,13 +853,13 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1056,13 +942,13 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1101,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1145,13 +1031,13 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1187,7 +1073,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1234,13 +1120,13 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1276,10 +1162,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1323,13 +1209,13 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1365,13 +1251,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -1412,13 +1298,13 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1501,13 +1387,13 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1543,10 +1429,10 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1590,13 +1476,13 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1632,13 +1518,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1679,13 +1565,13 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1727,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1768,13 +1654,13 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1810,13 +1696,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1857,13 +1743,13 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1899,10 +1785,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1946,13 +1832,13 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1988,13 +1874,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -2035,13 +1921,13 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2077,10 +1963,10 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2124,13 +2010,13 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2166,10 +2052,10 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2213,13 +2099,13 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2255,13 +2141,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -2302,13 +2188,13 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2350,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2391,13 +2277,13 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2433,13 +2319,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2480,13 +2366,13 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2525,10 +2411,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2569,13 +2455,13 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2611,13 +2497,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z22">
         <v>6</v>
@@ -2658,13 +2544,13 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2700,13 +2586,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2747,13 +2633,13 @@
         <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2792,7 +2678,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2836,13 +2722,13 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2878,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2925,13 +2811,13 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2967,10 +2853,10 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -3014,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -3056,7 +2942,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -3103,13 +2989,13 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3145,13 +3031,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3192,13 +3078,13 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3234,10 +3120,10 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3281,10 +3167,10 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3323,7 +3209,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3370,13 +3256,13 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3412,13 +3298,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>5</v>
@@ -3459,13 +3345,13 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3501,13 +3387,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3548,13 +3434,13 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3590,13 +3476,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>6</v>
@@ -3759,13 +3645,13 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -3827,13 +3713,13 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -3895,13 +3781,13 @@
         <v>95</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -3963,13 +3849,13 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -4031,13 +3917,13 @@
         <v>90</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -4102,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -4167,7 +4053,7 @@
         <v>95</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4235,13 +4121,13 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -4303,13 +4189,13 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4371,13 +4257,13 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4439,13 +4325,13 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4507,13 +4393,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4575,13 +4461,13 @@
         <v>90</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4643,13 +4529,13 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4711,13 +4597,13 @@
         <v>90</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4779,13 +4665,13 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4847,13 +4733,13 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4915,13 +4801,13 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4983,13 +4869,13 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5051,13 +4937,13 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -5119,13 +5005,13 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5187,13 +5073,13 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -5255,13 +5141,13 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -5323,13 +5209,13 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -5391,13 +5277,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -5459,13 +5345,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -5527,10 +5413,10 @@
         <v>80</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -5595,13 +5481,13 @@
         <v>90</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -5663,13 +5549,13 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -5731,13 +5617,13 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -5789,6 +5675,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5839,11 +5727,11 @@
       <c r="E2">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>26.67</v>
-      </c>
-      <c r="G2">
-        <v>73.33</v>
+      <c r="F2" s="2">
+        <v>26.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>73.3</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -5851,7 +5739,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5871,11 +5759,11 @@
       <c r="E3">
         <v>19</v>
       </c>
-      <c r="F3">
-        <v>36.67</v>
-      </c>
-      <c r="G3">
-        <v>63.33</v>
+      <c r="F3" s="2">
+        <v>36.7</v>
+      </c>
+      <c r="G3" s="2">
+        <v>63.3</v>
       </c>
       <c r="H3">
         <v>5.6</v>
@@ -5883,7 +5771,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5898,30 +5786,30 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>40</v>
+        <v>11</v>
+      </c>
+      <c r="F4" s="2">
+        <v>63.3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>36.7</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5930,30 +5818,30 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>80</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>73.3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>26.7</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5962,30 +5850,30 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>83.33</v>
-      </c>
-      <c r="G6">
-        <v>16.67</v>
+        <v>6</v>
+      </c>
+      <c r="F6" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" s="2">
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5994,30 +5882,30 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>93.33</v>
-      </c>
-      <c r="G7">
-        <v>6.67</v>
+        <v>5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>83.3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>16.7</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
@@ -6026,24 +5914,24 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>96.67</v>
-      </c>
-      <c r="G8">
-        <v>3.33</v>
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>93.3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>6.7</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6088,548 +5976,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920396</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920263</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920262</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920402</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920264</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920403</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920404</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920409</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920265</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920411</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920405</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920266</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920268</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920270</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920271</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920272</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920367</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920273</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920406</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920276</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920281</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920277</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920395</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920279</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920407</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920282</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920283</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920285</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920286</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>140</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920288</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6664,13 +6011,13 @@
         <v>22330051920262</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6687,13 +6034,13 @@
         <v>22330051920262</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6710,13 +6057,13 @@
         <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6733,13 +6080,13 @@
         <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6753,16 +6100,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920367</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6776,16 +6123,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920270</v>
+        <v>22330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6802,13 +6149,13 @@
         <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6825,13 +6172,13 @@
         <v>22330051920276</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6848,13 +6195,13 @@
         <v>22330051920277</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6871,13 +6218,13 @@
         <v>22330051920277</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6891,22 +6238,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920282</v>
+        <v>22330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6914,22 +6261,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920282</v>
+        <v>22330051920409</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6937,22 +6284,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920285</v>
+        <v>22330051920411</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6960,16 +6307,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920285</v>
+        <v>22330051920272</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -6983,16 +6330,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920264</v>
+        <v>22330051920273</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7006,22 +6353,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920409</v>
+        <v>22330051920407</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7029,16 +6376,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920411</v>
+        <v>22330051920285</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -7052,22 +6399,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920268</v>
+        <v>22330051920286</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
         <v>101</v>
       </c>
-      <c r="D19" t="s">
-        <v>125</v>
-      </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -7075,116 +6422,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920272</v>
+        <v>22330051920288</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
         <v>102</v>
       </c>
-      <c r="D20" t="s">
-        <v>128</v>
-      </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920273</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920407</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920286</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920288</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -185,24 +185,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -218,115 +218,97 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>OLMEDO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>MIA</t>
   </si>
   <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
     <t>SERGIO FARITH</t>
   </si>
   <si>
-    <t>ERIK</t>
-  </si>
-  <si>
     <t>OSCAR</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
     <t>QUETZALY</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
 </sst>
 </file>
@@ -868,10 +850,10 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -913,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -957,10 +939,10 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1046,10 +1028,10 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1088,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1135,10 +1117,10 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1180,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1224,10 +1206,10 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1266,10 +1248,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1313,10 +1295,10 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1402,10 +1384,10 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1491,10 +1473,10 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1533,10 +1515,10 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1580,10 +1562,10 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1625,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1669,10 +1651,10 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1711,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1758,10 +1740,10 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1847,10 +1829,10 @@
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1936,10 +1918,10 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1978,10 +1960,10 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2025,10 +2007,10 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2114,10 +2096,10 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2156,10 +2138,10 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2203,10 +2185,10 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2245,7 +2227,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2292,10 +2274,10 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2334,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2381,10 +2363,10 @@
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2423,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2470,10 +2452,10 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2512,10 +2494,10 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2559,10 +2541,10 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2648,10 +2630,10 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2690,10 +2672,10 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2737,10 +2719,10 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2782,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2826,10 +2808,10 @@
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2915,10 +2897,10 @@
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2960,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3004,10 +2986,10 @@
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3046,7 +3028,7 @@
         <v>7</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>6</v>
@@ -3093,10 +3075,10 @@
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3135,7 +3117,7 @@
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3182,10 +3164,10 @@
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3271,10 +3253,10 @@
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3313,7 +3295,7 @@
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3360,10 +3342,10 @@
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3402,10 +3384,10 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3449,10 +3431,10 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3491,10 +3473,10 @@
         <v>9</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3660,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3728,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3796,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3864,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3932,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4000,10 +3982,10 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4071,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4136,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4204,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4272,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4340,10 +4322,10 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4408,10 +4390,10 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4476,10 +4458,10 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4544,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4612,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4680,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4748,10 +4730,10 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4816,10 +4798,10 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4884,10 +4866,10 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4952,10 +4934,10 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5020,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5088,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5156,10 +5138,10 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5224,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5292,10 +5274,10 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5360,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5428,10 +5410,10 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5496,10 +5478,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5564,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -5632,10 +5614,10 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -5713,7 +5695,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5722,19 +5704,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2">
-        <v>26.7</v>
+        <v>36.7</v>
       </c>
       <c r="G2" s="2">
-        <v>73.3</v>
+        <v>63.3</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5745,7 +5727,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5754,19 +5736,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>36.7</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2">
-        <v>63.3</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5841,7 +5823,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5850,19 +5832,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5873,7 +5855,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5882,19 +5864,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5976,7 +5958,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6008,22 +5990,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920262</v>
+        <v>22330051920263</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6031,19 +6013,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920262</v>
+        <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -6054,22 +6036,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920262</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6077,22 +6059,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920262</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6100,22 +6082,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920367</v>
+        <v>22330051920409</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6123,22 +6105,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920367</v>
+        <v>22330051920409</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6146,22 +6128,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920276</v>
+        <v>22330051920265</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6169,22 +6151,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920276</v>
+        <v>22330051920265</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6192,22 +6174,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920277</v>
+        <v>22330051920411</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6215,22 +6197,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920277</v>
+        <v>22330051920411</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6238,19 +6220,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920264</v>
+        <v>22330051920276</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
@@ -6261,19 +6243,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920409</v>
+        <v>22330051920276</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>56</v>
@@ -6284,22 +6266,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920411</v>
+        <v>22330051920282</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6307,22 +6289,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920272</v>
+        <v>22330051920282</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6330,19 +6312,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920273</v>
+        <v>22330051920272</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>55</v>
@@ -6353,19 +6335,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920407</v>
+        <v>22330051920367</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
@@ -6376,22 +6358,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920285</v>
+        <v>22330051920277</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -6399,47 +6381,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920286</v>
+        <v>22330051920285</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>55</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920288</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -224,58 +224,61 @@
     <t>BACILIO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>OLMEDO</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
+    <t>EVANGELISTA</t>
   </si>
   <si>
     <t>------</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>TEZOCO</t>
   </si>
   <si>
     <t>MIA</t>
@@ -284,31 +287,31 @@
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
     <t>CARLOS DAVID</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
     <t>SERGIO FARITH</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
     <t>OSCAR</t>
   </si>
   <si>
-    <t>QUETZALY</t>
+    <t>MARISOL</t>
   </si>
 </sst>
 </file>
@@ -844,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -933,7 +936,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1022,7 +1025,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1111,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1200,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1289,7 +1292,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1378,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1420,7 +1423,7 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1467,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1509,7 +1512,7 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1556,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1645,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1734,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1823,7 +1826,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1865,7 +1868,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -1912,7 +1915,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1954,7 +1957,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2001,7 +2004,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2090,7 +2093,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2179,7 +2182,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2221,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2268,7 +2271,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2310,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2357,7 +2360,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2446,7 +2449,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2535,7 +2538,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2624,7 +2627,7 @@
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2713,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2802,7 +2805,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2891,7 +2894,7 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2980,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -3069,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3158,7 +3161,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3247,7 +3250,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3289,7 +3292,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3336,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3425,7 +3428,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3467,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>9</v>
@@ -3636,7 +3639,7 @@
         <v>96</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3704,7 +3707,7 @@
         <v>96</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3772,7 +3775,7 @@
         <v>96</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3840,7 +3843,7 @@
         <v>96</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -3908,7 +3911,7 @@
         <v>96</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -3976,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -4044,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -4112,7 +4115,7 @@
         <v>96</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -4180,7 +4183,7 @@
         <v>96</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -4248,7 +4251,7 @@
         <v>96</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -4316,7 +4319,7 @@
         <v>96</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -4384,7 +4387,7 @@
         <v>96</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -4452,7 +4455,7 @@
         <v>96</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -4520,7 +4523,7 @@
         <v>96</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -4588,7 +4591,7 @@
         <v>96</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -4656,7 +4659,7 @@
         <v>96</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -4724,7 +4727,7 @@
         <v>96</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -4792,7 +4795,7 @@
         <v>96</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -4860,7 +4863,7 @@
         <v>96</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -4928,7 +4931,7 @@
         <v>96</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4996,7 +4999,7 @@
         <v>96</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -5064,7 +5067,7 @@
         <v>96</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -5132,7 +5135,7 @@
         <v>96</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -5200,7 +5203,7 @@
         <v>80</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -5268,7 +5271,7 @@
         <v>96</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -5336,7 +5339,7 @@
         <v>96</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -5404,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -5472,7 +5475,7 @@
         <v>96</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -5540,7 +5543,7 @@
         <v>96</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -5608,7 +5611,7 @@
         <v>96</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -5716,7 +5719,7 @@
         <v>63.3</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5958,7 +5961,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5999,7 +6002,7 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6022,7 +6025,7 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6045,7 +6048,7 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6068,7 +6071,7 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6082,7 +6085,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920409</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -6091,7 +6094,7 @@
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6105,7 +6108,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920409</v>
+        <v>22330051920265</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6114,7 +6117,7 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6128,16 +6131,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6151,16 +6154,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920411</v>
+        <v>22330051920276</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
@@ -6183,7 +6186,7 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6197,7 +6200,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920411</v>
+        <v>22330051920276</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
@@ -6206,7 +6209,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6220,22 +6223,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920276</v>
+        <v>22330051920282</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6243,22 +6246,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920276</v>
+        <v>22330051920282</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6266,22 +6269,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920282</v>
+        <v>22330051920409</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6289,16 +6292,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920282</v>
+        <v>22330051920367</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -6312,16 +6315,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920272</v>
+        <v>22330051920273</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6335,22 +6338,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920367</v>
+        <v>22330051920277</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6358,47 +6361,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920277</v>
+        <v>22330051920288</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920285</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>6</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -939,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -981,7 +981,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1028,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1070,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1117,7 +1117,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>6</v>
@@ -1159,7 +1159,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1206,7 +1206,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1426,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1473,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -1562,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1604,7 +1604,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1651,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1740,7 +1740,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -1829,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>7</v>
@@ -2007,7 +2007,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>7</v>
@@ -2138,7 +2138,7 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -2274,7 +2274,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>7</v>
@@ -2363,7 +2363,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>7</v>
@@ -2452,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>7</v>
@@ -2494,7 +2494,7 @@
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2541,7 +2541,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -2583,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>7</v>
@@ -2719,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -2808,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -2897,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N27">
         <v>5</v>
@@ -2986,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>7</v>
@@ -3075,7 +3075,7 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>7</v>
@@ -3158,13 +3158,13 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -3253,7 +3253,7 @@
         <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>9</v>
@@ -3342,7 +3342,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>7</v>
@@ -3431,7 +3431,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>7</v>
@@ -3642,7 +3642,7 @@
         <v>85</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3710,7 +3710,7 @@
         <v>90</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="N5">
         <v>60</v>
@@ -3778,7 +3778,7 @@
         <v>95</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3846,7 +3846,7 @@
         <v>85</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="N7">
         <v>90</v>
@@ -3914,7 +3914,7 @@
         <v>105</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3982,7 +3982,7 @@
         <v>70</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -4050,7 +4050,7 @@
         <v>50</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>105</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>95</v>
@@ -4186,7 +4186,7 @@
         <v>105</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>75</v>
@@ -4254,7 +4254,7 @@
         <v>105</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4322,7 +4322,7 @@
         <v>85</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N14">
         <v>60</v>
@@ -4390,7 +4390,7 @@
         <v>110</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>110</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4526,7 +4526,7 @@
         <v>105</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N17">
         <v>90</v>
@@ -4594,7 +4594,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4662,7 +4662,7 @@
         <v>110</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
         <v>80</v>
@@ -4730,7 +4730,7 @@
         <v>105</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
         <v>95</v>
@@ -4798,7 +4798,7 @@
         <v>105</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>95</v>
@@ -4866,7 +4866,7 @@
         <v>105</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
         <v>90</v>
@@ -4934,7 +4934,7 @@
         <v>95</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N23">
         <v>90</v>
@@ -5002,7 +5002,7 @@
         <v>105</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
         <v>95</v>
@@ -5070,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>70</v>
@@ -5138,7 +5138,7 @@
         <v>90</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
         <v>70</v>
@@ -5274,7 +5274,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>90</v>
@@ -5342,7 +5342,7 @@
         <v>110</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>95</v>
@@ -5404,13 +5404,13 @@
         <v>68</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L30">
         <v>60</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="N30">
         <v>50</v>
@@ -5478,7 +5478,7 @@
         <v>110</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -5546,7 +5546,7 @@
         <v>95</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
         <v>90</v>
@@ -5614,7 +5614,7 @@
         <v>105</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
         <v>95</v>
@@ -5899,19 +5899,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="G8" s="2">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -3615,13 +3615,13 @@
         <v>84</v>
       </c>
       <c r="D4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>70</v>
@@ -3633,43 +3633,43 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L4">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>85</v>
       </c>
-      <c r="M4">
-        <v>120</v>
-      </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
       <c r="O4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3683,13 +3683,13 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -3701,43 +3701,43 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L5">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="M5">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N5">
+        <v>70</v>
+      </c>
+      <c r="O5">
         <v>90</v>
       </c>
-      <c r="M5">
-        <v>93.3</v>
-      </c>
-      <c r="N5">
-        <v>60</v>
-      </c>
-      <c r="O5">
-        <v>80</v>
-      </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3751,13 +3751,13 @@
         <v>92</v>
       </c>
       <c r="D6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="F6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>70</v>
@@ -3772,40 +3772,40 @@
         <v>92</v>
       </c>
       <c r="K6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>95</v>
+        <v>81.8</v>
       </c>
       <c r="M6">
-        <v>93.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O6">
         <v>95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3819,13 +3819,13 @@
         <v>88</v>
       </c>
       <c r="D7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="F7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>80</v>
@@ -3834,46 +3834,46 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L7">
+        <v>79.5</v>
+      </c>
+      <c r="M7">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N7">
         <v>85</v>
       </c>
-      <c r="M7">
-        <v>93.3</v>
-      </c>
-      <c r="N7">
-        <v>90</v>
-      </c>
       <c r="O7">
+        <v>87.5</v>
+      </c>
+      <c r="P7">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="Q7">
+        <v>84</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>79.5</v>
+      </c>
+      <c r="T7">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="U7">
         <v>85</v>
       </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
       <c r="V7">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3887,13 +3887,13 @@
         <v>96</v>
       </c>
       <c r="D8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>80</v>
@@ -3905,43 +3905,43 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3955,10 +3955,10 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="E9">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -3970,46 +3970,46 @@
         <v>65</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="L9">
+        <v>59.1</v>
+      </c>
+      <c r="M9">
+        <v>41.7</v>
+      </c>
+      <c r="N9">
+        <v>47.5</v>
+      </c>
+      <c r="O9">
         <v>70</v>
       </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>45</v>
-      </c>
-      <c r="O9">
-        <v>75</v>
-      </c>
       <c r="P9">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>59.1</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4023,13 +4023,13 @@
         <v>92</v>
       </c>
       <c r="D10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="F10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>80</v>
@@ -4038,46 +4038,46 @@
         <v>95</v>
       </c>
       <c r="I10">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L10">
+        <v>63.6</v>
+      </c>
+      <c r="M10">
+        <v>83.3</v>
+      </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>85</v>
+      </c>
+      <c r="P10">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="Q10">
+        <v>46</v>
+      </c>
+      <c r="R10">
         <v>50</v>
       </c>
-      <c r="M10">
-        <v>80</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>75</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
       <c r="S10">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4091,61 +4091,61 @@
         <v>100</v>
       </c>
       <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J11">
         <v>96</v>
       </c>
-      <c r="E11">
-        <v>110</v>
-      </c>
-      <c r="F11">
-        <v>120</v>
-      </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
-      <c r="I11">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="J11">
-        <v>92</v>
-      </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>97.7</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>97.5</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q11">
         <v>96</v>
       </c>
-      <c r="L11">
-        <v>105</v>
-      </c>
-      <c r="M11">
-        <v>120</v>
-      </c>
-      <c r="N11">
-        <v>95</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4159,13 +4159,13 @@
         <v>96</v>
       </c>
       <c r="D12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>80</v>
@@ -4174,46 +4174,46 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J12">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4227,13 +4227,13 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -4242,19 +4242,19 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J13">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K13">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4263,25 +4263,25 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4295,13 +4295,13 @@
         <v>96</v>
       </c>
       <c r="D14">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -4310,46 +4310,46 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J14">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K14">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="L14">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M14">
-        <v>113.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N14">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4363,13 +4363,13 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -4384,13 +4384,13 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4399,25 +4399,25 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4431,13 +4431,13 @@
         <v>92</v>
       </c>
       <c r="D16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>70</v>
@@ -4449,43 +4449,43 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
+        <v>95.5</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>85</v>
+      </c>
+      <c r="O16">
+        <v>95</v>
+      </c>
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
         <v>96</v>
       </c>
-      <c r="L16">
-        <v>110</v>
-      </c>
-      <c r="M16">
-        <v>120</v>
-      </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4499,13 +4499,13 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -4514,46 +4514,46 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K17">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="M17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4567,13 +4567,13 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>85</v>
@@ -4585,43 +4585,43 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>93.2</v>
+      </c>
+      <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>92.5</v>
+      </c>
+      <c r="O18">
+        <v>92.5</v>
+      </c>
+      <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
         <v>96</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>120</v>
-      </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>95</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4635,13 +4635,13 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -4656,40 +4656,40 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O19">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4703,13 +4703,13 @@
         <v>92</v>
       </c>
       <c r="D20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>85</v>
@@ -4718,46 +4718,46 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J20">
         <v>92</v>
       </c>
       <c r="K20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="M20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4771,13 +4771,13 @@
         <v>96</v>
       </c>
       <c r="D21">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E21">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F21">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G21">
         <v>85</v>
@@ -4786,46 +4786,46 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J21">
         <v>96</v>
       </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>95.5</v>
+      </c>
+      <c r="M21">
+        <v>97.2</v>
+      </c>
+      <c r="N21">
+        <v>90</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="Q21">
         <v>96</v>
       </c>
-      <c r="L21">
-        <v>105</v>
-      </c>
-      <c r="M21">
-        <v>120</v>
-      </c>
-      <c r="N21">
-        <v>95</v>
-      </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4839,13 +4839,13 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -4854,46 +4854,46 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J22">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4907,13 +4907,13 @@
         <v>96</v>
       </c>
       <c r="D23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E23">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="F23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -4925,43 +4925,43 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L23">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>95</v>
       </c>
-      <c r="M23">
-        <v>120</v>
-      </c>
-      <c r="N23">
-        <v>90</v>
-      </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4975,13 +4975,13 @@
         <v>96</v>
       </c>
       <c r="D24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -4990,46 +4990,46 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J24">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>105</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5043,13 +5043,13 @@
         <v>96</v>
       </c>
       <c r="D25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F25">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G25">
         <v>90</v>
@@ -5058,46 +5058,46 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J25">
+        <v>88</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="M25">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="N25">
         <v>80</v>
       </c>
-      <c r="K25">
-        <v>96</v>
-      </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
-        <v>120</v>
-      </c>
-      <c r="N25">
-        <v>70</v>
-      </c>
       <c r="O25">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5111,13 +5111,13 @@
         <v>92</v>
       </c>
       <c r="D26">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>90</v>
@@ -5126,46 +5126,46 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J26">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K26">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L26">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>80</v>
+      </c>
+      <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="Q26">
         <v>90</v>
       </c>
-      <c r="M26">
-        <v>120</v>
-      </c>
-      <c r="N26">
-        <v>70</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5179,13 +5179,13 @@
         <v>84</v>
       </c>
       <c r="D27">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="E27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G27">
         <v>55</v>
@@ -5194,46 +5194,46 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>91.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="J27">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K27">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="L27">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="N27">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5247,13 +5247,13 @@
         <v>96</v>
       </c>
       <c r="D28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F28">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G28">
         <v>95</v>
@@ -5262,46 +5262,46 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J28">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5315,13 +5315,13 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E29">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F29">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G29">
         <v>90</v>
@@ -5330,46 +5330,46 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K29">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>110</v>
+        <v>97.7</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N29">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5383,13 +5383,13 @@
         <v>84</v>
       </c>
       <c r="D30">
-        <v>76</v>
+        <v>79.2</v>
       </c>
       <c r="E30">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F30">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -5398,46 +5398,46 @@
         <v>80</v>
       </c>
       <c r="I30">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K30">
-        <v>60</v>
+        <v>70.8</v>
       </c>
       <c r="L30">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="M30">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="N30">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="O30">
         <v>80</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5451,13 +5451,13 @@
         <v>96</v>
       </c>
       <c r="D31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>90</v>
@@ -5466,46 +5466,46 @@
         <v>90</v>
       </c>
       <c r="I31">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J31">
         <v>96</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>95</v>
+      </c>
+      <c r="O31">
+        <v>95</v>
+      </c>
+      <c r="P31">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q31">
         <v>96</v>
       </c>
-      <c r="L31">
-        <v>110</v>
-      </c>
-      <c r="M31">
-        <v>120</v>
-      </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5519,13 +5519,13 @@
         <v>96</v>
       </c>
       <c r="D32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -5534,46 +5534,46 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J32">
         <v>96</v>
       </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>93.2</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>95</v>
+      </c>
+      <c r="O32">
+        <v>97.5</v>
+      </c>
+      <c r="P32">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q32">
         <v>96</v>
       </c>
-      <c r="L32">
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>93.2</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
         <v>95</v>
       </c>
-      <c r="M32">
-        <v>120</v>
-      </c>
-      <c r="N32">
-        <v>90</v>
-      </c>
-      <c r="O32">
-        <v>95</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
       <c r="V32">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5587,13 +5587,13 @@
         <v>92</v>
       </c>
       <c r="D33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="F33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>85</v>
@@ -5602,46 +5602,46 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J33">
         <v>92</v>
       </c>
       <c r="K33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -188,12 +188,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -221,27 +221,27 @@
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -251,30 +251,30 @@
     <t>FIERROS</t>
   </si>
   <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
@@ -284,28 +284,28 @@
     <t>MIA</t>
   </si>
   <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
     <t>KATIA PAOLA</t>
   </si>
   <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
     <t>ERIK</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
   </si>
   <si>
     <t>OSCAR</t>
@@ -862,7 +862,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -874,7 +874,7 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -883,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -895,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -951,7 +951,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -963,7 +963,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -972,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1040,7 +1040,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1052,7 +1052,7 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1073,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1129,7 +1129,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1218,7 +1218,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1230,7 +1230,7 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1307,7 +1307,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1319,7 +1319,7 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1396,7 +1396,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1408,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1417,7 +1417,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1497,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1518,7 +1518,7 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1586,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1595,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1663,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1675,7 +1675,7 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1684,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1696,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1752,7 +1752,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1764,7 +1764,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1785,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1841,7 +1841,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1853,7 +1853,7 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1930,7 +1930,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1942,7 +1942,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -2019,7 +2019,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2031,7 +2031,7 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2108,7 +2108,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2120,7 +2120,7 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2197,7 +2197,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2286,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2298,7 +2298,7 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2387,7 +2387,7 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2464,7 +2464,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2476,7 +2476,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2553,7 +2553,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2565,7 +2565,7 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2586,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2642,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2654,7 +2654,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2663,7 +2663,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2731,7 +2731,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2820,7 +2820,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2832,7 +2832,7 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2909,7 +2909,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2921,7 +2921,7 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2998,7 +2998,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3010,7 +3010,7 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3031,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>6</v>
@@ -3087,7 +3087,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3099,7 +3099,7 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3108,7 +3108,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3176,7 +3176,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3188,7 +3188,7 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3265,7 +3265,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3286,7 +3286,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3366,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3375,7 +3375,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3387,7 +3387,7 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3443,7 +3443,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3455,7 +3455,7 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3464,7 +3464,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3476,7 +3476,7 @@
         <v>9</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3654,7 +3654,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>86</v>
+        <v>83.8</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3666,7 +3666,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V4">
         <v>90</v>
@@ -3722,7 +3722,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3734,7 +3734,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="U5">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="V5">
         <v>90</v>
@@ -3790,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3802,7 +3802,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="U6">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V6">
         <v>95</v>
@@ -3858,7 +3858,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3870,7 +3870,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="U7">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V7">
         <v>87.5</v>
@@ -3926,7 +3926,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>94</v>
+        <v>92.5</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3938,7 +3938,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V8">
         <v>95</v>
@@ -3994,7 +3994,7 @@
         <v>24.3</v>
       </c>
       <c r="Q9">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R9">
         <v>20.8</v>
@@ -4006,7 +4006,7 @@
         <v>41.7</v>
       </c>
       <c r="U9">
-        <v>47.5</v>
+        <v>29.7</v>
       </c>
       <c r="V9">
         <v>70</v>
@@ -4062,7 +4062,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q10">
-        <v>46</v>
+        <v>28.8</v>
       </c>
       <c r="R10">
         <v>50</v>
@@ -4074,7 +4074,7 @@
         <v>83.3</v>
       </c>
       <c r="U10">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="V10">
         <v>85</v>
@@ -4130,7 +4130,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q11">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4142,7 +4142,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4198,7 +4198,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4210,7 +4210,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>77.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4266,7 +4266,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4278,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4334,7 +4334,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>86</v>
+        <v>88.8</v>
       </c>
       <c r="R14">
         <v>93.8</v>
@@ -4346,7 +4346,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="U14">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V14">
         <v>95</v>
@@ -4470,7 +4470,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4482,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="V16">
         <v>95</v>
@@ -4538,7 +4538,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>98</v>
+        <v>91.3</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4550,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4606,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4618,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="V18">
         <v>92.5</v>
@@ -4674,7 +4674,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4686,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V19">
         <v>92.5</v>
@@ -4742,7 +4742,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q20">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4754,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4810,7 +4810,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4822,7 +4822,7 @@
         <v>97.2</v>
       </c>
       <c r="U21">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4878,7 +4878,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q22">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4890,7 +4890,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4946,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4958,7 +4958,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5014,7 +5014,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5026,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5082,7 +5082,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q25">
-        <v>88</v>
+        <v>87.5</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5094,7 +5094,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="U25">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V25">
         <v>92.5</v>
@@ -5150,7 +5150,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5162,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5218,7 +5218,7 @@
         <v>95.7</v>
       </c>
       <c r="Q27">
-        <v>82</v>
+        <v>51.3</v>
       </c>
       <c r="R27">
         <v>83.3</v>
@@ -5230,7 +5230,7 @@
         <v>41.7</v>
       </c>
       <c r="U27">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="V27">
         <v>92.5</v>
@@ -5286,7 +5286,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5298,7 +5298,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="U28">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="V28">
         <v>97.5</v>
@@ -5354,7 +5354,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5366,7 +5366,7 @@
         <v>97.2</v>
       </c>
       <c r="U29">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5422,7 +5422,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>76</v>
+        <v>52.5</v>
       </c>
       <c r="R30">
         <v>70.8</v>
@@ -5434,7 +5434,7 @@
         <v>77.8</v>
       </c>
       <c r="U30">
-        <v>62.5</v>
+        <v>51.6</v>
       </c>
       <c r="V30">
         <v>80</v>
@@ -5490,7 +5490,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q31">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="V31">
         <v>95</v>
@@ -5558,7 +5558,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q32">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5570,7 +5570,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="V32">
         <v>97.5</v>
@@ -5626,7 +5626,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="Q33">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5638,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5739,19 +5739,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>50</v>
+        <v>63.3</v>
       </c>
       <c r="G3" s="2">
-        <v>50</v>
+        <v>36.7</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5762,7 +5762,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5771,19 +5771,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>63.3</v>
+        <v>73.3</v>
       </c>
       <c r="G4" s="2">
-        <v>36.7</v>
+        <v>26.7</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>20</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5961,7 +5961,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6008,7 +6008,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -6077,7 +6077,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -6097,10 +6097,10 @@
         <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6120,10 +6120,10 @@
         <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920411</v>
+        <v>22330051920282</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>79</v>
@@ -6143,10 +6143,10 @@
         <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920411</v>
+        <v>22330051920282</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>79</v>
@@ -6166,10 +6166,10 @@
         <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6177,10 +6177,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920276</v>
+        <v>22330051920262</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
@@ -6200,22 +6200,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920276</v>
+        <v>22330051920411</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920282</v>
+        <v>22330051920367</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6246,16 +6246,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920282</v>
+        <v>22330051920273</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6269,22 +6269,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920409</v>
+        <v>22330051920276</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6292,22 +6292,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920367</v>
+        <v>22330051920277</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6315,16 +6315,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920273</v>
+        <v>22330051920288</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6333,52 +6333,6 @@
         <v>55</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920277</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920288</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -218,97 +218,109 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
   </si>
   <si>
     <t>MARISOL</t>
@@ -859,19 +871,19 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -886,13 +898,13 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -948,19 +960,19 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -969,7 +981,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1037,19 +1049,19 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1058,19 +1070,19 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1126,19 +1138,19 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1147,13 +1159,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1215,19 +1227,19 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1304,19 +1316,19 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -1393,19 +1405,19 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1426,7 +1438,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1482,19 +1494,19 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1503,7 +1515,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1571,19 +1583,19 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1592,19 +1604,19 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1660,19 +1672,19 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1681,13 +1693,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1749,19 +1761,19 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1770,19 +1782,19 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -1838,19 +1850,19 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1927,19 +1939,19 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1948,7 +1960,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1960,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2016,19 +2028,19 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2037,7 +2049,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2049,7 +2061,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -2105,19 +2117,19 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2126,13 +2138,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -2194,19 +2206,19 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2227,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2283,19 +2295,19 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2316,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -2372,19 +2384,19 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2461,19 +2473,19 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2488,13 +2500,13 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2550,19 +2562,19 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2639,19 +2651,19 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2666,13 +2678,13 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -2728,19 +2740,19 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2749,19 +2761,19 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -2817,19 +2829,19 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2838,19 +2850,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -2906,19 +2918,19 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2927,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2995,19 +3007,19 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -3022,13 +3034,13 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3084,19 +3096,19 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3105,7 +3117,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3173,19 +3185,19 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3262,19 +3274,19 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3283,7 +3295,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3351,19 +3363,19 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3384,7 +3396,7 @@
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3440,19 +3452,19 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3473,7 +3485,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>7</v>
@@ -3651,7 +3663,7 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q4">
         <v>83.8</v>
@@ -3719,7 +3731,7 @@
         <v>90</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="Q5">
         <v>87.5</v>
@@ -3731,7 +3743,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="T5">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="U5">
         <v>81.3</v>
@@ -3787,7 +3799,7 @@
         <v>95</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="Q6">
         <v>92.5</v>
@@ -3799,7 +3811,7 @@
         <v>81.8</v>
       </c>
       <c r="T6">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="U6">
         <v>84.40000000000001</v>
@@ -3855,7 +3867,7 @@
         <v>87.5</v>
       </c>
       <c r="P7">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q7">
         <v>87.5</v>
@@ -3867,7 +3879,7 @@
         <v>79.5</v>
       </c>
       <c r="T7">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="U7">
         <v>84.40000000000001</v>
@@ -3991,19 +4003,19 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q9">
         <v>8.800000000000001</v>
       </c>
       <c r="R9">
-        <v>20.8</v>
+        <v>13.9</v>
       </c>
       <c r="S9">
         <v>59.1</v>
       </c>
       <c r="T9">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="U9">
         <v>29.7</v>
@@ -4059,19 +4071,19 @@
         <v>85</v>
       </c>
       <c r="P10">
-        <v>92.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="Q10">
         <v>28.8</v>
       </c>
       <c r="R10">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="S10">
         <v>63.6</v>
       </c>
       <c r="T10">
-        <v>83.3</v>
+        <v>55.6</v>
       </c>
       <c r="U10">
         <v>25</v>
@@ -4127,7 +4139,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q11">
         <v>92.5</v>
@@ -4195,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="Q12">
         <v>91.3</v>
@@ -4263,7 +4275,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q13">
         <v>96.3</v>
@@ -4331,19 +4343,19 @@
         <v>95</v>
       </c>
       <c r="P14">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>88.8</v>
       </c>
       <c r="R14">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="S14">
         <v>84.09999999999999</v>
       </c>
       <c r="T14">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="U14">
         <v>84.40000000000001</v>
@@ -4467,7 +4479,7 @@
         <v>95</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q16">
         <v>96.3</v>
@@ -4535,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q17">
         <v>91.3</v>
@@ -4547,7 +4559,7 @@
         <v>95.5</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U17">
         <v>90.59999999999999</v>
@@ -4671,7 +4683,7 @@
         <v>92.5</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q19">
         <v>97.5</v>
@@ -4739,7 +4751,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q20">
         <v>92.5</v>
@@ -4807,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q21">
         <v>90</v>
@@ -4819,7 +4831,7 @@
         <v>95.5</v>
       </c>
       <c r="T21">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U21">
         <v>87.5</v>
@@ -4875,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Q22">
         <v>97.5</v>
@@ -5011,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q24">
         <v>93.8</v>
@@ -5091,7 +5103,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="T25">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="U25">
         <v>84.40000000000001</v>
@@ -5147,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>88.8</v>
@@ -5159,7 +5171,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="U26">
         <v>84.40000000000001</v>
@@ -5215,19 +5227,19 @@
         <v>92.5</v>
       </c>
       <c r="P27">
-        <v>95.7</v>
+        <v>59.8</v>
       </c>
       <c r="Q27">
         <v>51.3</v>
       </c>
       <c r="R27">
-        <v>83.3</v>
+        <v>55.6</v>
       </c>
       <c r="S27">
         <v>81.8</v>
       </c>
       <c r="T27">
-        <v>41.7</v>
+        <v>42.6</v>
       </c>
       <c r="U27">
         <v>25</v>
@@ -5283,7 +5295,7 @@
         <v>97.5</v>
       </c>
       <c r="P28">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="Q28">
         <v>91.3</v>
@@ -5295,7 +5307,7 @@
         <v>93.2</v>
       </c>
       <c r="T28">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="U28">
         <v>92.2</v>
@@ -5351,7 +5363,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="Q29">
         <v>95</v>
@@ -5363,7 +5375,7 @@
         <v>97.7</v>
       </c>
       <c r="T29">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U29">
         <v>92.2</v>
@@ -5419,19 +5431,19 @@
         <v>80</v>
       </c>
       <c r="P30">
-        <v>92.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="Q30">
         <v>52.5</v>
       </c>
       <c r="R30">
-        <v>70.8</v>
+        <v>47.2</v>
       </c>
       <c r="S30">
         <v>54.5</v>
       </c>
       <c r="T30">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="U30">
         <v>51.6</v>
@@ -5487,7 +5499,7 @@
         <v>95</v>
       </c>
       <c r="P31">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q31">
         <v>95</v>
@@ -5499,7 +5511,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U31">
         <v>93.8</v>
@@ -5555,7 +5567,7 @@
         <v>97.5</v>
       </c>
       <c r="P32">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q32">
         <v>96.3</v>
@@ -5623,7 +5635,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q33">
         <v>95</v>
@@ -5730,7 +5742,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5739,19 +5751,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>63.3</v>
+        <v>73.3</v>
       </c>
       <c r="G3" s="2">
-        <v>36.7</v>
+        <v>26.7</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5762,7 +5774,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5771,19 +5783,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="G4" s="2">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5794,7 +5806,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5803,19 +5815,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5826,7 +5838,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5835,19 +5847,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>76.7</v>
+        <v>86.7</v>
       </c>
       <c r="G6" s="2">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5858,7 +5870,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5867,19 +5879,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5899,19 +5911,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5961,7 +5973,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5993,22 +6005,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6016,22 +6028,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6039,16 +6051,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6062,22 +6074,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6085,22 +6097,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6108,22 +6120,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920270</v>
+        <v>22330051920265</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6131,22 +6143,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920282</v>
+        <v>22330051920405</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6154,22 +6166,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920282</v>
+        <v>22330051920405</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6177,7 +6189,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920262</v>
+        <v>22330051920270</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -6186,13 +6198,13 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6200,16 +6212,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920411</v>
+        <v>22330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6223,16 +6235,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920367</v>
+        <v>22330051920263</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -6246,16 +6258,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920273</v>
+        <v>22330051920262</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6269,16 +6281,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920276</v>
+        <v>22330051920411</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6292,22 +6304,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920277</v>
+        <v>22330051920367</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6315,16 +6327,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920288</v>
+        <v>22330051920273</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6333,6 +6345,75 @@
         <v>55</v>
       </c>
       <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920276</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920282</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920288</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -218,27 +218,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
     <t>OLMEDO</t>
   </si>
   <si>
@@ -254,15 +257,18 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>FIERROS</t>
   </si>
   <si>
@@ -287,28 +293,31 @@
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
   </si>
   <si>
     <t>SERGIO FARITH</t>
@@ -889,7 +898,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -910,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -978,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -999,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1067,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1088,7 +1097,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1156,7 +1165,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1245,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1334,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1423,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1512,7 +1521,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1601,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1690,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1711,7 +1720,7 @@
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1779,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1800,7 +1809,7 @@
         <v>6</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1868,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1957,7 +1966,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2046,7 +2055,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2135,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2224,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2313,7 +2322,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2334,7 +2343,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2402,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2423,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2491,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2512,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2580,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2601,7 +2610,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2669,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2690,7 +2699,7 @@
         <v>6</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2758,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2847,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2868,7 +2877,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2936,7 +2945,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -3025,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -3046,7 +3055,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3114,7 +3123,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3135,7 +3144,7 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3203,7 +3212,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3292,7 +3301,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3381,7 +3390,7 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3402,7 +3411,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3470,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3681,7 +3690,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3749,7 +3758,7 @@
         <v>81.3</v>
       </c>
       <c r="V5">
-        <v>90</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3817,7 +3826,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V6">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3885,7 +3894,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V7">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3953,7 +3962,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V8">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4021,7 +4030,7 @@
         <v>29.7</v>
       </c>
       <c r="V9">
-        <v>70</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4089,7 +4098,7 @@
         <v>25</v>
       </c>
       <c r="V10">
-        <v>85</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4361,7 +4370,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4497,7 +4506,7 @@
         <v>87.5</v>
       </c>
       <c r="V16">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4633,7 +4642,7 @@
         <v>92.2</v>
       </c>
       <c r="V18">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4701,7 +4710,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V19">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5109,7 +5118,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V25">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5245,7 +5254,7 @@
         <v>25</v>
       </c>
       <c r="V27">
-        <v>92.5</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5313,7 +5322,7 @@
         <v>92.2</v>
       </c>
       <c r="V28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5449,7 +5458,7 @@
         <v>51.6</v>
       </c>
       <c r="V30">
-        <v>80</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5517,7 +5526,7 @@
         <v>93.8</v>
       </c>
       <c r="V31">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5585,7 +5594,7 @@
         <v>93.8</v>
       </c>
       <c r="V32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5774,7 +5783,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5783,19 +5792,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5806,7 +5815,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5815,19 +5824,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="G5" s="2">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6005,16 +6014,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6028,22 +6037,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6051,16 +6060,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920402</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6074,16 +6083,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6097,22 +6106,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6120,22 +6129,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6143,16 +6152,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6166,22 +6175,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>22330051920395</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6189,22 +6198,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920270</v>
+        <v>21330051920396</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6212,16 +6221,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920270</v>
+        <v>22330051920263</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6235,16 +6244,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920263</v>
+        <v>22330051920262</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -6258,16 +6267,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920262</v>
+        <v>22330051920411</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6281,16 +6290,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920411</v>
+        <v>22330051920405</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6307,13 +6316,13 @@
         <v>22330051920367</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -6330,13 +6339,13 @@
         <v>22330051920273</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6353,13 +6362,13 @@
         <v>22330051920276</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -6376,13 +6385,13 @@
         <v>22330051920282</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -6399,13 +6408,13 @@
         <v>22330051920288</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>

--- a/grupos/2APV - Estadisticos 20222.xlsx
+++ b/grupos/2APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -218,121 +218,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GALINDO</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
     <t>BRANDON</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
 </sst>
 </file>
@@ -889,7 +817,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -910,7 +838,7 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -978,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1067,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1088,7 +1016,7 @@
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1156,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1177,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1245,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1266,7 +1194,7 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1334,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -1423,7 +1351,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -1512,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1601,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1690,7 +1618,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1711,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>9</v>
@@ -1779,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1800,7 +1728,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1868,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1957,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1978,7 +1906,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -2046,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -2135,7 +2063,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2156,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2224,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2313,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2334,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2402,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2423,7 +2351,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>6</v>
@@ -2491,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2580,7 +2508,7 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2601,7 +2529,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2669,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2758,7 +2686,7 @@
         <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2847,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2868,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>6</v>
@@ -2936,7 +2864,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -3025,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -3114,7 +3042,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -3135,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3203,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -3292,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3381,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3402,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3470,7 +3398,7 @@
         <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3491,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3681,7 +3609,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3749,7 +3677,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>86.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="T5">
         <v>92.59999999999999</v>
@@ -3817,7 +3745,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="T6">
         <v>92.59999999999999</v>
@@ -3885,7 +3813,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="T7">
         <v>92.59999999999999</v>
@@ -3953,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4021,7 +3949,7 @@
         <v>13.9</v>
       </c>
       <c r="S9">
-        <v>59.1</v>
+        <v>40.6</v>
       </c>
       <c r="T9">
         <v>27.8</v>
@@ -4089,7 +4017,7 @@
         <v>33.3</v>
       </c>
       <c r="S10">
-        <v>63.6</v>
+        <v>43.8</v>
       </c>
       <c r="T10">
         <v>55.6</v>
@@ -4157,7 +4085,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4225,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>97.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4293,7 +4221,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4361,7 +4289,7 @@
         <v>95.8</v>
       </c>
       <c r="S14">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T14">
         <v>92.59999999999999</v>
@@ -4497,7 +4425,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4565,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T17">
         <v>94.40000000000001</v>
@@ -4633,7 +4561,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4769,7 +4697,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4837,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T21">
         <v>98.09999999999999</v>
@@ -4905,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -4973,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5041,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5109,7 +5037,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="T25">
         <v>96.3</v>
@@ -5177,7 +5105,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T26">
         <v>81.5</v>
@@ -5245,7 +5173,7 @@
         <v>55.6</v>
       </c>
       <c r="S27">
-        <v>81.8</v>
+        <v>56.3</v>
       </c>
       <c r="T27">
         <v>42.6</v>
@@ -5313,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T28">
         <v>96.3</v>
@@ -5381,7 +5309,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T29">
         <v>98.09999999999999</v>
@@ -5449,7 +5377,7 @@
         <v>47.2</v>
       </c>
       <c r="S30">
-        <v>54.5</v>
+        <v>37.5</v>
       </c>
       <c r="T30">
         <v>85.2</v>
@@ -5585,7 +5513,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -5653,7 +5581,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -5719,7 +5647,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5728,19 +5656,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>36.7</v>
+        <v>73.3</v>
       </c>
       <c r="G2" s="2">
-        <v>63.3</v>
+        <v>26.7</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5751,7 +5679,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5772,7 +5700,7 @@
         <v>26.7</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5982,7 +5910,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6014,22 +5942,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920402</v>
+        <v>22330051920265</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6037,22 +5965,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920402</v>
+        <v>22330051920265</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6060,22 +5988,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6083,19 +6011,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>56</v>
@@ -6106,22 +6034,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920262</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6129,19 +6057,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920270</v>
+        <v>22330051920402</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -6155,274 +6083,21 @@
         <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920395</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920396</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920263</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920262</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920411</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920405</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920367</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920273</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920276</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920282</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920288</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>
